--- a/Decks/Hivelord.xlsx
+++ b/Decks/Hivelord.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F989C168-EB9E-43E2-B361-AA97B29AFF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD86BE56-A091-46F7-8AD2-0AD006632CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="78">
   <si>
     <t>Função</t>
   </si>
@@ -236,9 +236,6 @@
     <t>Swiftfoot Boots</t>
   </si>
   <si>
-    <t>Lightning Greaves</t>
-  </si>
-  <si>
     <t>Season of Growth</t>
   </si>
   <si>
@@ -270,6 +267,9 @@
   </si>
   <si>
     <t>Mutante</t>
+  </si>
+  <si>
+    <t>Rhythm of the Wild</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F52"/>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F53"/>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1285,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F55"/>
     </row>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F58"/>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F59"/>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F60"/>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F61"/>
     </row>
@@ -1441,11 +1441,13 @@
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>1</v>
-      </c>
-      <c r="C67" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D67" s="4" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67"/>
@@ -1456,9 +1458,11 @@
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C68" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D68" s="4" t="s">
         <v>65</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1491,7 +1495,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1505,7 +1509,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1518,7 +1522,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1531,7 +1535,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1545,7 +1549,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1562,7 +1566,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1578,7 +1582,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1594,7 +1598,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1610,7 +1614,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1626,7 +1630,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1639,7 +1643,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1653,7 +1657,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1666,7 +1670,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1680,7 +1684,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1694,7 +1698,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1708,7 +1712,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1722,7 +1726,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B87" s="5" t="b">
         <f>C87&lt;&gt;D87</f>
@@ -1736,7 +1740,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1750,7 +1754,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1764,7 +1768,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1778,7 +1782,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1792,7 +1796,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1805,7 +1809,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1819,7 +1823,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1833,7 +1837,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1846,7 +1850,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1860,7 +1864,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1874,7 +1878,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1898,7 +1902,7 @@
         <v>61</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">

--- a/Decks/Hivelord.xlsx
+++ b/Decks/Hivelord.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD86BE56-A091-46F7-8AD2-0AD006632CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E34454E-5409-4A91-BCE0-8D666B7739CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E60CFCF-D828-4F94-80E9-62CC112406F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="93">
   <si>
     <t>Função</t>
   </si>
@@ -270,6 +270,51 @@
   </si>
   <si>
     <t>Rhythm of the Wild</t>
+  </si>
+  <si>
+    <t>Bedevil</t>
+  </si>
+  <si>
+    <t>Sliver Hivelord</t>
+  </si>
+  <si>
+    <t>Command Tower</t>
+  </si>
+  <si>
+    <t>Exotic Orchard</t>
+  </si>
+  <si>
+    <t>Cinder Glade</t>
+  </si>
+  <si>
+    <t>Canopy Vista</t>
+  </si>
+  <si>
+    <t>Clifftop Retreat</t>
+  </si>
+  <si>
+    <t>Dragonskull Summit</t>
+  </si>
+  <si>
+    <t>Glacial Fortress</t>
+  </si>
+  <si>
+    <t>Hinterland Harbor</t>
+  </si>
+  <si>
+    <t>Sulfur Falls</t>
+  </si>
+  <si>
+    <t>Sunken Hollow</t>
+  </si>
+  <si>
+    <t>Rootbound Crag</t>
+  </si>
+  <si>
+    <t>Sodden Verdure</t>
+  </si>
+  <si>
+    <t>Avenge</t>
   </si>
 </sst>
 </file>
@@ -698,9 +743,12 @@
       </c>
       <c r="B2" s="5" t="b">
         <f>C2&lt;&gt;D2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -710,7 +758,12 @@
         <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -718,9 +771,12 @@
       </c>
       <c r="B4" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -730,7 +786,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -740,7 +801,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -750,7 +816,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -760,7 +831,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -830,7 +906,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -840,9 +921,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -850,9 +936,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -860,9 +951,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -870,9 +966,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -880,9 +981,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -892,7 +998,7 @@
       </c>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -902,7 +1008,7 @@
       </c>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -912,7 +1018,7 @@
       </c>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -922,7 +1028,7 @@
       </c>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -932,7 +1038,7 @@
       </c>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -942,7 +1048,7 @@
       </c>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -952,7 +1058,7 @@
       </c>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -962,7 +1068,7 @@
       </c>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -972,7 +1078,7 @@
       </c>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -982,7 +1088,7 @@
       </c>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -992,7 +1098,7 @@
       </c>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1078,9 +1184,11 @@
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C40" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="D40" s="4" t="s">
         <v>11</v>
       </c>
@@ -1240,9 +1348,11 @@
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C52" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="D52" s="4" t="s">
         <v>66</v>
       </c>
@@ -1268,9 +1378,11 @@
       </c>
       <c r="B54" s="5" t="b">
         <f>C54&lt;&gt;D54</f>
-        <v>1</v>
-      </c>
-      <c r="C54" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="D54" s="4" t="s">
         <v>74</v>
       </c>
@@ -1311,9 +1423,11 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C57" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D57" s="4" t="s">
         <v>43</v>
       </c>
@@ -1339,9 +1453,11 @@
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C59" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="D59" s="4" t="s">
         <v>70</v>
       </c>
@@ -1353,9 +1469,11 @@
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C60" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="D60" s="4" t="s">
         <v>71</v>
       </c>
@@ -1367,9 +1485,11 @@
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C61" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D61" s="4" t="s">
         <v>72</v>
       </c>
@@ -1383,7 +1503,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C62" s="4"/>
+      <c r="C62" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1394,7 +1519,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C63" s="4"/>
+      <c r="C63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -1513,10 +1643,15 @@
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C72" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="D72" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E72" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1526,9 +1661,11 @@
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C73" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="D73" s="4" t="s">
         <v>26</v>
       </c>
@@ -1539,9 +1676,11 @@
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C74" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="D74" s="4" t="s">
         <v>28</v>
       </c>
@@ -1553,14 +1692,16 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C75" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D75" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" t="s">
         <v>52</v>
-      </c>
-      <c r="E75" t="s">
-        <v>56</v>
       </c>
       <c r="F75" s="4"/>
     </row>
@@ -1570,15 +1711,14 @@
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C76" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="D76" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E76" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1586,14 +1726,16 @@
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C77" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="D77" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" t="s">
         <v>44</v>
-      </c>
-      <c r="E77" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -1602,14 +1744,16 @@
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C78" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="D78" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E78" t="s">
         <v>33</v>
-      </c>
-      <c r="E78" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,9 +1768,6 @@
       <c r="D79" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E79" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -1634,9 +1775,11 @@
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C80" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="D80" s="4" t="s">
         <v>29</v>
       </c>
@@ -1661,9 +1804,11 @@
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C82" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="D82" s="4" t="s">
         <v>32</v>
       </c>
@@ -1674,9 +1819,11 @@
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C83" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D83" s="4" t="s">
         <v>31</v>
       </c>
@@ -1716,9 +1863,11 @@
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C86" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="D86" s="4" t="s">
         <v>36</v>
       </c>
@@ -1744,9 +1893,11 @@
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C88" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="D88" s="4" t="s">
         <v>35</v>
       </c>
@@ -1758,9 +1909,11 @@
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C89" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="D89" s="4" t="s">
         <v>41</v>
       </c>
@@ -1772,9 +1925,11 @@
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C90" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="D90" t="s">
         <v>27</v>
       </c>
@@ -1786,9 +1941,11 @@
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C91" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="D91" s="4" t="s">
         <v>45</v>
       </c>
@@ -1800,9 +1957,11 @@
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C92" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="D92" s="4" t="s">
         <v>46</v>
       </c>
@@ -1813,9 +1972,11 @@
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C93" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="D93" s="4" t="s">
         <v>47</v>
       </c>
@@ -1827,9 +1988,11 @@
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C94" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="D94" s="4" t="s">
         <v>48</v>
       </c>
@@ -1841,9 +2004,11 @@
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C95" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="D95" s="4" t="s">
         <v>40</v>
       </c>
@@ -1854,9 +2019,11 @@
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C96" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="D96" s="4" t="s">
         <v>42</v>
       </c>
@@ -1868,9 +2035,11 @@
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C97" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="D97" s="4" t="s">
         <v>10</v>
       </c>
@@ -1895,9 +2064,11 @@
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C99" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="D99" s="4" t="s">
         <v>61</v>
       </c>
@@ -1911,9 +2082,11 @@
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C100" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="D100" s="4" t="s">
         <v>62</v>
       </c>
@@ -1924,9 +2097,11 @@
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C101" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="D101" s="4" t="s">
         <v>49</v>
       </c>
